--- a/StructureDefinition-mii-pr-molgen-genomic-study-analysis.xlsx
+++ b/StructureDefinition-mii-pr-molgen-genomic-study-analysis.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc1</t>
+    <t>2027.0.0-ballot.rc2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T06:24:08+00:00</t>
+    <t>2026-09-08T06:06:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-mii-pr-molgen-genomic-study-analysis.xlsx
+++ b/StructureDefinition-mii-pr-molgen-genomic-study-analysis.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2339" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2340" uniqueCount="454">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc2</t>
+    <t>2027.0.0-ballot.rc3</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,10 +57,13 @@
     <t>Experimental</t>
   </si>
   <si>
+    <t>false</t>
+  </si>
+  <si>
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-08T06:06:53+00:00</t>
+    <t>2026-09-11T14:33:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -118,9 +121,6 @@
   </si>
   <si>
     <t>Abstract</t>
-  </si>
-  <si>
-    <t>false</t>
   </si>
   <si>
     <t>Derivation</t>
@@ -1648,98 +1648,100 @@
       <c r="A7" t="s" s="2">
         <v>12</v>
       </c>
-      <c r="B7" s="2"/>
+      <c r="B7" t="s" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>13</v>
       </c>
     </row>
     <row r="20">
@@ -1921,10 +1923,10 @@
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
@@ -2004,7 +2006,7 @@
         <v>76</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG2" t="s" s="2">
         <v>77</v>
